--- a/FischerTropsch_Paper_Michi/Südafrika_FischerTropsch_2_Naphta_Brownfield_MH/Datenbank.xlsx
+++ b/FischerTropsch_Paper_Michi/Südafrika_FischerTropsch_2_Naphta_Brownfield_MH/Datenbank.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hem38994\Documents\GitHub\FENES_P2X\FischerTropsch_Paper_Michi\Südafrika_FischerTropsch_2_Naphta_Brownfield_MH\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6BB3633-EED0-46D4-9C07-DB97783FFA71}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F64AA6E-8338-40F6-970A-DE8E6EC57DB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-4455" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-6885" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Datenauswahl" sheetId="1" r:id="rId1"/>
@@ -1653,10 +1653,13 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1671,11 +1674,8 @@
     <xf numFmtId="0" fontId="5" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -2173,23 +2173,23 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:G74"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="10.88671875" style="2" customWidth="1"/>
-    <col min="2" max="2" width="18.6640625" style="29" customWidth="1"/>
-    <col min="3" max="3" width="36.21875" style="2" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.90625" style="2" customWidth="1"/>
+    <col min="2" max="2" width="18.6328125" style="29" customWidth="1"/>
+    <col min="3" max="3" width="36.1796875" style="2" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="21" style="2" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="19" style="10" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="40.77734375" style="2" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="20.77734375" style="2" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="20.77734375" style="2" customWidth="1"/>
-    <col min="9" max="9" width="13.88671875" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="40.81640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="20.81640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="20.81640625" style="2" customWidth="1"/>
+    <col min="9" max="9" width="13.90625" style="2" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="14" style="2" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="10.77734375" style="2" bestFit="1" customWidth="1"/>
-    <col min="12" max="16384" width="8.88671875" style="2"/>
+    <col min="11" max="11" width="10.81640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="12" max="16384" width="8.90625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A1" s="4" t="s">
         <v>69</v>
       </c>
@@ -2210,7 +2210,7 @@
       </c>
       <c r="G1" s="29"/>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2" s="37" t="s">
         <v>70</v>
       </c>
@@ -2230,7 +2230,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A3" s="38"/>
       <c r="B3" s="45"/>
       <c r="C3" s="2" t="s">
@@ -2246,7 +2246,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A4" s="38"/>
       <c r="B4" s="45"/>
       <c r="C4" s="2" t="s">
@@ -2262,7 +2262,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A5" s="38"/>
       <c r="B5" s="45"/>
       <c r="C5" s="2" t="s">
@@ -2278,7 +2278,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A6" s="38"/>
       <c r="B6" s="45"/>
       <c r="C6" s="2" t="s">
@@ -2294,7 +2294,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A7" s="38"/>
       <c r="B7" s="45"/>
       <c r="C7" s="2" t="s">
@@ -2310,7 +2310,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A8" s="38"/>
       <c r="B8" s="48" t="s">
         <v>330</v>
@@ -2328,7 +2328,7 @@
         <v>344</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A9" s="38"/>
       <c r="B9" s="45"/>
       <c r="C9" s="2" t="s">
@@ -2344,7 +2344,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A10" s="38"/>
       <c r="B10" s="45"/>
       <c r="C10" s="2" t="s">
@@ -2360,7 +2360,7 @@
         <v>341</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A11" s="38"/>
       <c r="B11" s="45"/>
       <c r="C11" s="2" t="s">
@@ -2376,7 +2376,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A12" s="38"/>
       <c r="B12" s="45"/>
       <c r="C12" s="2" t="s">
@@ -2392,7 +2392,7 @@
         <v>342</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A13" s="38"/>
       <c r="B13" s="45"/>
       <c r="C13" s="2" t="s">
@@ -2408,7 +2408,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A14" s="38"/>
       <c r="B14" s="45"/>
       <c r="C14" s="2" t="s">
@@ -2424,7 +2424,7 @@
         <v>370</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A15" s="38"/>
       <c r="B15" s="45"/>
       <c r="C15" s="2" t="s">
@@ -2440,7 +2440,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A16" s="38"/>
       <c r="B16" s="49"/>
       <c r="C16" s="13" t="s">
@@ -2456,7 +2456,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A17" s="38"/>
       <c r="B17" s="48" t="s">
         <v>262</v>
@@ -2474,7 +2474,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A18" s="38"/>
       <c r="B18" s="45"/>
       <c r="C18" s="2" t="s">
@@ -2490,7 +2490,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A19" s="38"/>
       <c r="B19" s="45"/>
       <c r="C19" s="2" t="s">
@@ -2506,7 +2506,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A20" s="38"/>
       <c r="B20" s="45"/>
       <c r="C20" s="2" t="s">
@@ -2522,7 +2522,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A21" s="38"/>
       <c r="B21" s="45"/>
       <c r="C21" s="2" t="s">
@@ -2538,7 +2538,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A22" s="38"/>
       <c r="B22" s="49"/>
       <c r="C22" s="13" t="s">
@@ -2554,7 +2554,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A23" s="38"/>
       <c r="B23" s="41" t="s">
         <v>229</v>
@@ -2572,7 +2572,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A24" s="38"/>
       <c r="B24" s="41"/>
       <c r="C24" s="2" t="s">
@@ -2588,7 +2588,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A25" s="38"/>
       <c r="B25" s="41"/>
       <c r="C25" s="2" t="s">
@@ -2604,7 +2604,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A26" s="38"/>
       <c r="B26" s="41"/>
       <c r="C26" s="2" t="s">
@@ -2620,7 +2620,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A27" s="38"/>
       <c r="B27" s="41"/>
       <c r="C27" s="2" t="s">
@@ -2636,7 +2636,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="28" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A28" s="38"/>
       <c r="B28" s="41"/>
       <c r="C28" s="2" t="s">
@@ -2652,7 +2652,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A29" s="37" t="s">
         <v>71</v>
       </c>
@@ -2672,7 +2672,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A30" s="38"/>
       <c r="B30" s="41"/>
       <c r="C30" s="2" t="s">
@@ -2688,7 +2688,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A31" s="38"/>
       <c r="B31" s="41"/>
       <c r="C31" s="2" t="s">
@@ -2704,7 +2704,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A32" s="38"/>
       <c r="B32" s="41"/>
       <c r="C32" s="2" t="s">
@@ -2720,7 +2720,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A33" s="38"/>
       <c r="B33" s="41"/>
       <c r="C33" s="2" t="s">
@@ -2736,7 +2736,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A34" s="38"/>
       <c r="B34" s="41"/>
       <c r="C34" s="2" t="s">
@@ -2752,7 +2752,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A35" s="38"/>
       <c r="B35" s="41"/>
       <c r="C35" s="2" t="s">
@@ -2768,7 +2768,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="36" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A36" s="38"/>
       <c r="B36" s="42"/>
       <c r="C36" s="13" t="s">
@@ -2784,7 +2784,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A37" s="38"/>
       <c r="B37" s="43" t="s">
         <v>305</v>
@@ -2802,7 +2802,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A38" s="38"/>
       <c r="B38" s="41"/>
       <c r="C38" s="2" t="s">
@@ -2818,7 +2818,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A39" s="38"/>
       <c r="B39" s="41"/>
       <c r="C39" s="2" t="s">
@@ -2834,7 +2834,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A40" s="38"/>
       <c r="B40" s="41"/>
       <c r="C40" s="2" t="s">
@@ -2850,7 +2850,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A41" s="38"/>
       <c r="B41" s="41"/>
       <c r="C41" s="2" t="s">
@@ -2866,7 +2866,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A42" s="38"/>
       <c r="B42" s="41"/>
       <c r="C42" s="2" t="s">
@@ -2882,7 +2882,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A43" s="38"/>
       <c r="B43" s="41"/>
       <c r="C43" s="2" t="s">
@@ -2898,7 +2898,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A44" s="38"/>
       <c r="B44" s="41"/>
       <c r="C44" s="13" t="s">
@@ -2914,7 +2914,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A45" s="38"/>
       <c r="B45" s="43" t="s">
         <v>201</v>
@@ -2932,7 +2932,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A46" s="38"/>
       <c r="B46" s="45"/>
       <c r="C46" s="2" t="s">
@@ -2949,7 +2949,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A47" s="38"/>
       <c r="B47" s="45"/>
       <c r="C47" s="2" t="s">
@@ -2965,7 +2965,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A48" s="38"/>
       <c r="B48" s="45"/>
       <c r="C48" s="2" t="s">
@@ -2981,7 +2981,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A49" s="38"/>
       <c r="B49" s="45"/>
       <c r="C49" s="2" t="s">
@@ -2997,7 +2997,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A50" s="38"/>
       <c r="B50" s="45"/>
       <c r="C50" s="2" t="s">
@@ -3013,7 +3013,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A51" s="38"/>
       <c r="B51" s="45"/>
       <c r="C51" s="2" t="s">
@@ -3029,7 +3029,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A52" s="38"/>
       <c r="B52" s="45"/>
       <c r="C52" s="2" t="s">
@@ -3045,7 +3045,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A53" s="38"/>
       <c r="B53" s="45"/>
       <c r="C53" s="2" t="s">
@@ -3061,7 +3061,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="54" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A54" s="39"/>
       <c r="B54" s="46"/>
       <c r="C54" s="17" t="s">
@@ -3077,7 +3077,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A55" s="37" t="s">
         <v>72</v>
       </c>
@@ -3097,7 +3097,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A56" s="38"/>
       <c r="B56" s="43" t="s">
         <v>4</v>
@@ -3115,7 +3115,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A57" s="38"/>
       <c r="B57" s="41"/>
       <c r="C57" s="2" t="s">
@@ -3131,7 +3131,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A58" s="38"/>
       <c r="B58" s="41"/>
       <c r="C58" s="2" t="s">
@@ -3147,7 +3147,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A59" s="38"/>
       <c r="B59" s="41"/>
       <c r="C59" s="2" t="s">
@@ -3163,7 +3163,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A60" s="38"/>
       <c r="B60" s="41"/>
       <c r="C60" s="2" t="s">
@@ -3179,7 +3179,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A61" s="38"/>
       <c r="B61" s="41"/>
       <c r="C61" s="2" t="s">
@@ -3195,7 +3195,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A62" s="38"/>
       <c r="B62" s="42"/>
       <c r="C62" s="13" t="s">
@@ -3211,7 +3211,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A63" s="38"/>
       <c r="B63" s="43" t="s">
         <v>5</v>
@@ -3229,7 +3229,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A64" s="38"/>
       <c r="B64" s="41"/>
       <c r="C64" s="2" t="s">
@@ -3245,7 +3245,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A65" s="38"/>
       <c r="B65" s="41"/>
       <c r="C65" s="2" t="s">
@@ -3261,7 +3261,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A66" s="38"/>
       <c r="B66" s="41"/>
       <c r="C66" s="2" t="s">
@@ -3277,7 +3277,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A67" s="38"/>
       <c r="B67" s="41"/>
       <c r="C67" s="2" t="s">
@@ -3293,7 +3293,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A68" s="38"/>
       <c r="B68" s="41"/>
       <c r="C68" s="2" t="s">
@@ -3309,7 +3309,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A69" s="39"/>
       <c r="B69" s="44"/>
       <c r="C69" s="17" t="s">
@@ -3325,7 +3325,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A70" s="37" t="s">
         <v>76</v>
       </c>
@@ -3339,13 +3339,13 @@
         <v>78</v>
       </c>
       <c r="E70" s="33">
-        <v>-1E-4</v>
+        <v>0</v>
       </c>
       <c r="F70" s="32" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A71" s="38"/>
       <c r="B71" s="29" t="s">
         <v>288</v>
@@ -3357,13 +3357,13 @@
         <v>290</v>
       </c>
       <c r="E71" s="10">
-        <v>-1E-4</v>
+        <v>0</v>
       </c>
       <c r="F71" s="2" t="s">
         <v>314</v>
       </c>
     </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A72" s="38"/>
       <c r="B72" s="34" t="s">
         <v>79</v>
@@ -3381,7 +3381,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A73" s="38"/>
       <c r="B73" s="34" t="s">
         <v>371</v>
@@ -3399,7 +3399,7 @@
         <v>374</v>
       </c>
     </row>
-    <row r="74" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A74" s="39"/>
       <c r="B74" s="5" t="s">
         <v>331</v>
@@ -3443,18 +3443,18 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{83AB2E79-6F94-41B5-A552-C40EC4890194}">
   <dimension ref="A1:F149"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.54296875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="14.5546875" style="2" customWidth="1"/>
-    <col min="2" max="2" width="30.33203125" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="38.5546875" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="50.77734375" style="2" customWidth="1"/>
-    <col min="5" max="5" width="46.109375" style="2" customWidth="1"/>
-    <col min="6" max="6" width="37.5546875" style="2" customWidth="1"/>
-    <col min="7" max="16384" width="11.5546875" style="2"/>
+    <col min="1" max="1" width="14.54296875" style="2" customWidth="1"/>
+    <col min="2" max="2" width="30.36328125" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="38.54296875" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="50.81640625" style="2" customWidth="1"/>
+    <col min="5" max="5" width="46.08984375" style="2" customWidth="1"/>
+    <col min="6" max="6" width="37.54296875" style="2" customWidth="1"/>
+    <col min="7" max="16384" width="11.54296875" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A1" s="4" t="s">
         <v>69</v>
       </c>
@@ -3474,7 +3474,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A2" s="37" t="s">
         <v>70</v>
       </c>
@@ -3492,7 +3492,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A3" s="38"/>
       <c r="B3" s="45"/>
       <c r="C3" s="2" t="s">
@@ -3506,7 +3506,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A4" s="38"/>
       <c r="B4" s="45"/>
       <c r="C4" s="2" t="s">
@@ -3520,7 +3520,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A5" s="38"/>
       <c r="B5" s="45"/>
       <c r="C5" s="2" t="s">
@@ -3534,7 +3534,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A6" s="38"/>
       <c r="B6" s="45"/>
       <c r="C6" s="2" t="s">
@@ -3548,7 +3548,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A7" s="38"/>
       <c r="B7" s="45"/>
       <c r="C7" s="2" t="s">
@@ -3562,7 +3562,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A8" s="38"/>
       <c r="B8" s="45"/>
       <c r="C8" s="2" t="s">
@@ -3576,7 +3576,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A9" s="38"/>
       <c r="B9" s="45"/>
       <c r="C9" s="2" t="s">
@@ -3590,7 +3590,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A10" s="38"/>
       <c r="B10" s="45"/>
       <c r="C10" s="2" t="s">
@@ -3604,14 +3604,14 @@
         <v>149</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A11" s="38"/>
       <c r="B11" s="45"/>
       <c r="E11" s="10"/>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A12" s="38"/>
-      <c r="B12" s="56" t="s">
+      <c r="B12" s="50" t="s">
         <v>364</v>
       </c>
       <c r="C12" s="12" t="s">
@@ -3625,7 +3625,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A13" s="38"/>
       <c r="B13" s="51"/>
       <c r="C13" s="2" t="s">
@@ -3639,7 +3639,7 @@
         <v>358</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A14" s="38"/>
       <c r="B14" s="51"/>
       <c r="C14" s="2" t="s">
@@ -3653,7 +3653,7 @@
         <v>377</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A15" s="38"/>
       <c r="B15" s="51"/>
       <c r="C15" s="2" t="s">
@@ -3667,7 +3667,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A16" s="38"/>
       <c r="B16" s="51"/>
       <c r="C16" s="2" t="s">
@@ -3681,7 +3681,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A17" s="38"/>
       <c r="B17" s="51"/>
       <c r="C17" s="2" t="s">
@@ -3695,7 +3695,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A18" s="38"/>
       <c r="B18" s="51"/>
       <c r="C18" s="2" t="s">
@@ -3709,7 +3709,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A19" s="38"/>
       <c r="B19" s="51"/>
       <c r="C19" s="2" t="s">
@@ -3723,7 +3723,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A20" s="38"/>
       <c r="B20" s="51"/>
       <c r="C20" s="2" t="s">
@@ -3737,7 +3737,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A21" s="38"/>
       <c r="B21" s="51"/>
       <c r="C21" s="2" t="s">
@@ -3751,7 +3751,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A22" s="38"/>
       <c r="B22" s="51"/>
       <c r="C22" s="2" t="s">
@@ -3765,15 +3765,15 @@
         <v>149</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A23" s="38"/>
-      <c r="B23" s="57"/>
+      <c r="B23" s="52"/>
       <c r="C23" s="13"/>
       <c r="D23" s="13"/>
       <c r="E23" s="14"/>
       <c r="F23" s="13"/>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A24" s="38"/>
       <c r="B24" s="48" t="s">
         <v>262</v>
@@ -3789,7 +3789,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A25" s="38"/>
       <c r="B25" s="45"/>
       <c r="C25" s="2" t="s">
@@ -3803,7 +3803,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A26" s="38"/>
       <c r="B26" s="45"/>
       <c r="C26" s="2" t="s">
@@ -3817,7 +3817,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A27" s="38"/>
       <c r="B27" s="45"/>
       <c r="C27" s="2" t="s">
@@ -3831,7 +3831,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A28" s="38"/>
       <c r="B28" s="45"/>
       <c r="C28" s="2" t="s">
@@ -3845,7 +3845,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A29" s="38"/>
       <c r="B29" s="45"/>
       <c r="C29" s="2" t="s">
@@ -3859,7 +3859,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A30" s="38"/>
       <c r="B30" s="45"/>
       <c r="C30" s="2" t="s">
@@ -3873,7 +3873,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A31" s="38"/>
       <c r="B31" s="45"/>
       <c r="C31" s="2" t="s">
@@ -3887,7 +3887,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A32" s="38"/>
       <c r="B32" s="45"/>
       <c r="C32" s="2" t="s">
@@ -3901,7 +3901,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A33" s="38"/>
       <c r="B33" s="49"/>
       <c r="C33" s="13"/>
@@ -3909,7 +3909,7 @@
       <c r="E33" s="14"/>
       <c r="F33" s="13"/>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A34" s="38"/>
       <c r="B34" s="41" t="s">
         <v>229</v>
@@ -3925,7 +3925,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A35" s="38"/>
       <c r="B35" s="41"/>
       <c r="C35" s="2" t="s">
@@ -3939,7 +3939,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A36" s="38"/>
       <c r="B36" s="41"/>
       <c r="C36" s="2" t="s">
@@ -3953,7 +3953,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A37" s="38"/>
       <c r="B37" s="41"/>
       <c r="C37" s="2" t="s">
@@ -3967,7 +3967,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A38" s="38"/>
       <c r="B38" s="41"/>
       <c r="C38" s="2" t="s">
@@ -3981,7 +3981,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A39" s="38"/>
       <c r="B39" s="41"/>
       <c r="C39" s="2" t="s">
@@ -3995,7 +3995,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A40" s="38"/>
       <c r="B40" s="41"/>
       <c r="C40" s="2" t="s">
@@ -4009,7 +4009,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A41" s="38"/>
       <c r="B41" s="41"/>
       <c r="C41" s="2" t="s">
@@ -4023,7 +4023,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A42" s="38"/>
       <c r="B42" s="41"/>
       <c r="C42" s="2" t="s">
@@ -4037,7 +4037,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A43" s="38"/>
       <c r="B43" s="41"/>
       <c r="C43" s="2" t="s">
@@ -4051,12 +4051,12 @@
         <v>149</v>
       </c>
     </row>
-    <row r="44" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A44" s="38"/>
       <c r="B44" s="41"/>
       <c r="E44" s="10"/>
     </row>
-    <row r="45" spans="1:6" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:6" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A45" s="37" t="s">
         <v>71</v>
       </c>
@@ -4074,7 +4074,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A46" s="38"/>
       <c r="B46" s="41"/>
       <c r="C46" s="2" t="s">
@@ -4088,7 +4088,7 @@
         <v>393</v>
       </c>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A47" s="38"/>
       <c r="B47" s="41"/>
       <c r="C47" s="2" t="s">
@@ -4102,7 +4102,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A48" s="38"/>
       <c r="B48" s="41"/>
       <c r="C48" s="2" t="s">
@@ -4116,7 +4116,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A49" s="38"/>
       <c r="B49" s="41"/>
       <c r="C49" s="2" t="s">
@@ -4130,7 +4130,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A50" s="38"/>
       <c r="B50" s="41"/>
       <c r="C50" s="2" t="s">
@@ -4144,7 +4144,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A51" s="38"/>
       <c r="B51" s="41"/>
       <c r="C51" s="2" t="s">
@@ -4158,7 +4158,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A52" s="38"/>
       <c r="B52" s="41"/>
       <c r="C52" s="2" t="s">
@@ -4172,7 +4172,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A53" s="38"/>
       <c r="B53" s="41"/>
       <c r="C53" s="2" t="s">
@@ -4186,7 +4186,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A54" s="38"/>
       <c r="B54" s="42"/>
       <c r="C54" s="13"/>
@@ -4194,7 +4194,7 @@
       <c r="E54" s="14"/>
       <c r="F54" s="13"/>
     </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A55" s="38"/>
       <c r="B55" s="41" t="s">
         <v>305</v>
@@ -4210,7 +4210,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A56" s="38"/>
       <c r="B56" s="41"/>
       <c r="C56" s="2" t="s">
@@ -4224,7 +4224,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A57" s="38"/>
       <c r="B57" s="41"/>
       <c r="C57" s="2" t="s">
@@ -4238,7 +4238,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A58" s="38"/>
       <c r="B58" s="41"/>
       <c r="C58" s="2" t="s">
@@ -4252,7 +4252,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A59" s="38"/>
       <c r="B59" s="41"/>
       <c r="C59" s="2" t="s">
@@ -4266,7 +4266,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A60" s="38"/>
       <c r="B60" s="41"/>
       <c r="C60" s="2" t="s">
@@ -4280,7 +4280,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A61" s="38"/>
       <c r="B61" s="41"/>
       <c r="C61" s="2" t="s">
@@ -4294,7 +4294,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A62" s="38"/>
       <c r="B62" s="41"/>
       <c r="C62" s="2" t="s">
@@ -4308,7 +4308,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A63" s="38"/>
       <c r="B63" s="41"/>
       <c r="C63" s="2" t="s">
@@ -4322,12 +4322,12 @@
         <v>149</v>
       </c>
     </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A64" s="38"/>
       <c r="B64" s="42"/>
       <c r="E64" s="10"/>
     </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A65" s="38"/>
       <c r="B65" s="43" t="s">
         <v>6</v>
@@ -4343,7 +4343,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A66" s="38"/>
       <c r="B66" s="41"/>
       <c r="C66" s="2" t="s">
@@ -4357,7 +4357,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A67" s="38"/>
       <c r="B67" s="45"/>
       <c r="C67" s="2" t="s">
@@ -4371,7 +4371,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A68" s="38"/>
       <c r="B68" s="45"/>
       <c r="C68" s="2" t="s">
@@ -4385,7 +4385,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A69" s="38"/>
       <c r="B69" s="45"/>
       <c r="C69" s="2" t="s">
@@ -4399,7 +4399,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A70" s="38"/>
       <c r="B70" s="45"/>
       <c r="C70" s="2" t="s">
@@ -4413,7 +4413,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A71" s="38"/>
       <c r="B71" s="45"/>
       <c r="C71" s="2" t="s">
@@ -4427,7 +4427,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A72" s="38"/>
       <c r="B72" s="45"/>
       <c r="C72" s="2" t="s">
@@ -4441,7 +4441,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A73" s="38"/>
       <c r="B73" s="45"/>
       <c r="C73" s="2" t="s">
@@ -4455,7 +4455,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A74" s="38"/>
       <c r="B74" s="45"/>
       <c r="C74" s="2" t="s">
@@ -4469,7 +4469,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A75" s="38"/>
       <c r="B75" s="45"/>
       <c r="C75" s="2" t="s">
@@ -4483,7 +4483,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="76" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A76" s="39"/>
       <c r="B76" s="46"/>
       <c r="C76" s="17"/>
@@ -4491,7 +4491,7 @@
       <c r="E76" s="18"/>
       <c r="F76" s="17"/>
     </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A77" s="37" t="s">
         <v>72</v>
       </c>
@@ -4509,7 +4509,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A78" s="38"/>
       <c r="B78" s="45"/>
       <c r="C78" s="2" t="s">
@@ -4523,12 +4523,12 @@
         <v>149</v>
       </c>
     </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A79" s="38"/>
       <c r="B79" s="49"/>
       <c r="E79" s="8"/>
     </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A80" s="38"/>
       <c r="B80" s="43" t="s">
         <v>4</v>
@@ -4544,7 +4544,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A81" s="38"/>
       <c r="B81" s="41"/>
       <c r="C81" s="2" t="s">
@@ -4558,7 +4558,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A82" s="38"/>
       <c r="B82" s="41"/>
       <c r="C82" s="2" t="s">
@@ -4572,7 +4572,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A83" s="38"/>
       <c r="B83" s="41"/>
       <c r="C83" s="2" t="s">
@@ -4586,7 +4586,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A84" s="38"/>
       <c r="B84" s="41"/>
       <c r="C84" s="2" t="s">
@@ -4600,7 +4600,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A85" s="38"/>
       <c r="B85" s="41"/>
       <c r="C85" s="2" t="s">
@@ -4614,7 +4614,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A86" s="38"/>
       <c r="B86" s="41"/>
       <c r="C86" s="2" t="s">
@@ -4628,7 +4628,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A87" s="38"/>
       <c r="B87" s="41"/>
       <c r="C87" s="2" t="s">
@@ -4642,7 +4642,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="88" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A88" s="38"/>
       <c r="B88" s="41"/>
       <c r="C88" s="2" t="s">
@@ -4656,11 +4656,11 @@
         <v>149</v>
       </c>
     </row>
-    <row r="89" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A89" s="38"/>
       <c r="B89" s="42"/>
     </row>
-    <row r="90" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A90" s="38"/>
       <c r="B90" s="43" t="s">
         <v>5</v>
@@ -4676,7 +4676,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="91" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A91" s="38"/>
       <c r="B91" s="41"/>
       <c r="C91" s="2" t="s">
@@ -4690,7 +4690,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A92" s="38"/>
       <c r="B92" s="41"/>
       <c r="C92" s="2" t="s">
@@ -4704,7 +4704,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="93" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A93" s="38"/>
       <c r="B93" s="41"/>
       <c r="C93" s="2" t="s">
@@ -4718,7 +4718,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="94" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A94" s="38"/>
       <c r="B94" s="41"/>
       <c r="C94" s="2" t="s">
@@ -4732,7 +4732,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="95" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A95" s="38"/>
       <c r="B95" s="41"/>
       <c r="C95" s="2" t="s">
@@ -4746,7 +4746,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A96" s="38"/>
       <c r="B96" s="41"/>
       <c r="C96" s="2" t="s">
@@ -4760,7 +4760,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="97" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A97" s="38"/>
       <c r="B97" s="41"/>
       <c r="C97" s="2" t="s">
@@ -4774,7 +4774,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="98" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A98" s="38"/>
       <c r="B98" s="41"/>
       <c r="C98" s="2" t="s">
@@ -4788,11 +4788,11 @@
         <v>149</v>
       </c>
     </row>
-    <row r="99" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A99" s="39"/>
       <c r="B99" s="44"/>
     </row>
-    <row r="100" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A100" s="37" t="s">
         <v>76</v>
       </c>
@@ -4810,7 +4810,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="101" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A101" s="38"/>
       <c r="B101" s="45"/>
       <c r="C101" s="2" t="s">
@@ -4824,7 +4824,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="102" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A102" s="38"/>
       <c r="B102" s="45"/>
       <c r="C102" s="2" t="s">
@@ -4838,7 +4838,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="103" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A103" s="38"/>
       <c r="B103" s="49"/>
       <c r="C103" s="13"/>
@@ -4846,7 +4846,7 @@
       <c r="E103" s="14"/>
       <c r="F103" s="13"/>
     </row>
-    <row r="104" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A104" s="38"/>
       <c r="B104" s="48" t="s">
         <v>292</v>
@@ -4862,7 +4862,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="105" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A105" s="38"/>
       <c r="B105" s="45"/>
       <c r="C105" s="2" t="s">
@@ -4876,7 +4876,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="106" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A106" s="38"/>
       <c r="B106" s="45"/>
       <c r="C106" s="2" t="s">
@@ -4890,12 +4890,12 @@
         <v>149</v>
       </c>
     </row>
-    <row r="107" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A107" s="38"/>
       <c r="B107" s="49"/>
       <c r="E107" s="10"/>
     </row>
-    <row r="108" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A108" s="38"/>
       <c r="B108" s="48" t="s">
         <v>79</v>
@@ -4911,7 +4911,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="109" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A109" s="38"/>
       <c r="B109" s="45"/>
       <c r="C109" s="2" t="s">
@@ -4925,7 +4925,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="110" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A110" s="38"/>
       <c r="B110" s="49"/>
       <c r="C110" s="13"/>
@@ -4933,9 +4933,9 @@
       <c r="E110" s="14"/>
       <c r="F110" s="13"/>
     </row>
-    <row r="111" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A111" s="38"/>
-      <c r="B111" s="53" t="s">
+      <c r="B111" s="54" t="s">
         <v>371</v>
       </c>
       <c r="C111" s="12" t="s">
@@ -4949,9 +4949,9 @@
         <v>377</v>
       </c>
     </row>
-    <row r="112" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A112" s="38"/>
-      <c r="B112" s="54"/>
+      <c r="B112" s="55"/>
       <c r="C112" s="2" t="s">
         <v>376</v>
       </c>
@@ -4963,15 +4963,15 @@
         <v>149</v>
       </c>
     </row>
-    <row r="113" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A113" s="38"/>
-      <c r="B113" s="55"/>
+      <c r="B113" s="56"/>
       <c r="C113" s="13"/>
       <c r="D113" s="13"/>
       <c r="E113" s="14"/>
       <c r="F113" s="13"/>
     </row>
-    <row r="114" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A114" s="38"/>
       <c r="B114" s="51" t="s">
         <v>331</v>
@@ -4987,7 +4987,7 @@
         <v>358</v>
       </c>
     </row>
-    <row r="115" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A115" s="38"/>
       <c r="B115" s="51"/>
       <c r="C115" s="2" t="s">
@@ -5001,15 +5001,15 @@
         <v>149</v>
       </c>
     </row>
-    <row r="116" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A116" s="39"/>
-      <c r="B116" s="52"/>
+      <c r="B116" s="53"/>
       <c r="C116" s="17"/>
       <c r="D116" s="17"/>
       <c r="E116" s="18"/>
       <c r="F116" s="17"/>
     </row>
-    <row r="117" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A117" s="37" t="s">
         <v>163</v>
       </c>
@@ -5027,7 +5027,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="118" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A118" s="38"/>
       <c r="B118" s="45"/>
       <c r="C118" s="2" t="s">
@@ -5040,7 +5040,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="119" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A119" s="38"/>
       <c r="B119" s="49"/>
       <c r="C119" s="13"/>
@@ -5048,7 +5048,7 @@
       <c r="E119" s="13"/>
       <c r="F119" s="13"/>
     </row>
-    <row r="120" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A120" s="38"/>
       <c r="B120" s="48" t="s">
         <v>183</v>
@@ -5063,7 +5063,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="121" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A121" s="38"/>
       <c r="B121" s="45"/>
       <c r="C121" s="2" t="s">
@@ -5076,7 +5076,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="122" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A122" s="38"/>
       <c r="B122" s="45"/>
       <c r="C122" s="2" t="s">
@@ -5089,7 +5089,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="123" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A123" s="38"/>
       <c r="B123" s="45"/>
       <c r="C123" s="2" t="s">
@@ -5102,7 +5102,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="124" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A124" s="38"/>
       <c r="B124" s="45"/>
       <c r="C124" s="2" t="s">
@@ -5115,7 +5115,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="125" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A125" s="38"/>
       <c r="B125" s="45"/>
       <c r="C125" s="2" t="s">
@@ -5128,11 +5128,11 @@
         <v>149</v>
       </c>
     </row>
-    <row r="126" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A126" s="38"/>
       <c r="B126" s="49"/>
     </row>
-    <row r="127" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A127" s="38"/>
       <c r="B127" s="48" t="s">
         <v>206</v>
@@ -5148,7 +5148,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="128" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A128" s="38"/>
       <c r="B128" s="45"/>
       <c r="C128" s="2" t="s">
@@ -5161,7 +5161,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="129" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A129" s="38"/>
       <c r="B129" s="45"/>
       <c r="C129" s="2" t="s">
@@ -5174,7 +5174,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="130" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A130" s="38"/>
       <c r="B130" s="45"/>
       <c r="C130" s="2" t="s">
@@ -5187,7 +5187,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="131" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A131" s="38"/>
       <c r="B131" s="45"/>
       <c r="C131" s="2" t="s">
@@ -5200,7 +5200,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="132" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A132" s="38"/>
       <c r="B132" s="45"/>
       <c r="C132" s="21" t="s">
@@ -5214,7 +5214,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="133" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A133" s="38"/>
       <c r="B133" s="45"/>
       <c r="C133" s="21" t="s">
@@ -5228,7 +5228,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="134" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A134" s="38"/>
       <c r="B134" s="45"/>
       <c r="C134" s="2" t="s">
@@ -5241,7 +5241,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="135" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A135" s="38"/>
       <c r="B135" s="45"/>
       <c r="C135" s="2" t="s">
@@ -5254,7 +5254,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="136" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A136" s="38"/>
       <c r="B136" s="45"/>
       <c r="C136" s="2" t="s">
@@ -5267,7 +5267,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="137" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A137" s="38"/>
       <c r="B137" s="45"/>
       <c r="C137" s="21" t="s">
@@ -5281,7 +5281,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="138" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A138" s="38"/>
       <c r="B138" s="45"/>
       <c r="C138" s="21" t="s">
@@ -5295,7 +5295,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="139" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A139" s="38"/>
       <c r="B139" s="45"/>
       <c r="C139" s="21" t="s">
@@ -5309,7 +5309,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="140" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A140" s="38"/>
       <c r="B140" s="45"/>
       <c r="C140" s="21" t="s">
@@ -5323,7 +5323,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="141" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A141" s="38"/>
       <c r="B141" s="49"/>
       <c r="C141" s="21"/>
@@ -5331,7 +5331,7 @@
       <c r="E141" s="21"/>
       <c r="F141" s="21"/>
     </row>
-    <row r="142" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A142" s="38"/>
       <c r="B142" s="48" t="s">
         <v>222</v>
@@ -5347,7 +5347,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="143" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A143" s="38"/>
       <c r="B143" s="45"/>
       <c r="C143" s="2" t="s">
@@ -5360,7 +5360,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="144" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A144" s="38"/>
       <c r="B144" s="45"/>
       <c r="C144" s="2" t="s">
@@ -5373,7 +5373,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="145" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A145" s="38"/>
       <c r="B145" s="45"/>
       <c r="C145" s="21" t="s">
@@ -5387,7 +5387,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="146" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A146" s="38"/>
       <c r="B146" s="45"/>
       <c r="C146" s="21" t="s">
@@ -5401,7 +5401,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="147" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A147" s="38"/>
       <c r="B147" s="49"/>
       <c r="C147" s="13"/>
@@ -5409,9 +5409,9 @@
       <c r="E147" s="13"/>
       <c r="F147" s="13"/>
     </row>
-    <row r="148" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A148" s="38"/>
-      <c r="B148" s="50" t="s">
+      <c r="B148" s="57" t="s">
         <v>386</v>
       </c>
       <c r="C148" s="2" t="s">
@@ -5424,9 +5424,9 @@
         <v>345</v>
       </c>
     </row>
-    <row r="149" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A149" s="38"/>
-      <c r="B149" s="50"/>
+      <c r="B149" s="57"/>
       <c r="C149" s="2" t="s">
         <v>388</v>
       </c>
@@ -5439,15 +5439,12 @@
     </row>
   </sheetData>
   <mergeCells count="25">
-    <mergeCell ref="A2:A44"/>
-    <mergeCell ref="B2:B11"/>
-    <mergeCell ref="B12:B23"/>
-    <mergeCell ref="B34:B44"/>
-    <mergeCell ref="A45:A76"/>
-    <mergeCell ref="B65:B76"/>
-    <mergeCell ref="B24:B33"/>
-    <mergeCell ref="B45:B54"/>
-    <mergeCell ref="B55:B64"/>
+    <mergeCell ref="B142:B147"/>
+    <mergeCell ref="B148:B149"/>
+    <mergeCell ref="A117:A149"/>
+    <mergeCell ref="B117:B119"/>
+    <mergeCell ref="B127:B141"/>
+    <mergeCell ref="B120:B126"/>
     <mergeCell ref="B114:B116"/>
     <mergeCell ref="B77:B79"/>
     <mergeCell ref="A77:A99"/>
@@ -5458,12 +5455,15 @@
     <mergeCell ref="B104:B107"/>
     <mergeCell ref="B108:B110"/>
     <mergeCell ref="B111:B113"/>
-    <mergeCell ref="B142:B147"/>
-    <mergeCell ref="B148:B149"/>
-    <mergeCell ref="A117:A149"/>
-    <mergeCell ref="B117:B119"/>
-    <mergeCell ref="B127:B141"/>
-    <mergeCell ref="B120:B126"/>
+    <mergeCell ref="A2:A44"/>
+    <mergeCell ref="B2:B11"/>
+    <mergeCell ref="B12:B23"/>
+    <mergeCell ref="B34:B44"/>
+    <mergeCell ref="A45:A76"/>
+    <mergeCell ref="B65:B76"/>
+    <mergeCell ref="B24:B33"/>
+    <mergeCell ref="B45:B54"/>
+    <mergeCell ref="B55:B64"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -5473,57 +5473,57 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{93C614C4-2B7C-4798-B4E2-788104541F45}">
   <dimension ref="B1:B31"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="11.5546875" style="23"/>
+    <col min="2" max="2" width="11.54296875" style="23"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B1" s="23" t="s">
         <v>259</v>
       </c>
     </row>
-    <row r="2" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B2" s="23" t="s">
         <v>253</v>
       </c>
     </row>
-    <row r="22" spans="2:2" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:2" ht="14.5" x14ac:dyDescent="0.35">
       <c r="B22" s="26" t="s">
         <v>261</v>
       </c>
     </row>
-    <row r="24" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B24" s="23" t="s">
         <v>260</v>
       </c>
     </row>
-    <row r="26" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B26" s="23" t="s">
         <v>254</v>
       </c>
     </row>
-    <row r="27" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B27" s="23" t="s">
         <v>255</v>
       </c>
     </row>
-    <row r="28" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B28" s="23" t="s">
         <v>256</v>
       </c>
     </row>
-    <row r="29" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="29" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B29" s="24" t="s">
         <v>257</v>
       </c>
     </row>
-    <row r="30" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="30" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B30" s="25" t="s">
         <v>258</v>
       </c>
     </row>
-    <row r="31" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="31" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B31" s="25"/>
     </row>
   </sheetData>
